--- a/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
+++ b/rules/CORE-000852/negative/01/data/unit-test-coreid-CG0330-negative.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000852\negative\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52217914-1D02-4209-B1CD-6E41C7235864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5F9056-9B41-4D64-91A6-7D41888CB225}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="858" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="30" r:id="rId1"/>
     <sheet name="Datasets" sheetId="2" r:id="rId2"/>
-    <sheet name="cm.xpt" sheetId="21" r:id="rId3"/>
-    <sheet name="ce.xpt" sheetId="22" r:id="rId4"/>
-    <sheet name="lb.xpt" sheetId="23" r:id="rId5"/>
-    <sheet name="fa.xpt" sheetId="24" r:id="rId6"/>
-    <sheet name="se.xpt" sheetId="25" r:id="rId7"/>
-    <sheet name="sv.xpt" sheetId="26" r:id="rId8"/>
-    <sheet name="vs.xpt" sheetId="31" r:id="rId9"/>
+    <sheet name="Validation" sheetId="32" r:id="rId3"/>
+    <sheet name="cm.xpt" sheetId="21" r:id="rId4"/>
+    <sheet name="ce.xpt" sheetId="22" r:id="rId5"/>
+    <sheet name="lb.xpt" sheetId="23" r:id="rId6"/>
+    <sheet name="fa.xpt" sheetId="24" r:id="rId7"/>
+    <sheet name="se.xpt" sheetId="25" r:id="rId8"/>
+    <sheet name="sv.xpt" sheetId="26" r:id="rId9"/>
+    <sheet name="vs.xpt" sheetId="31" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1038" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1046" uniqueCount="346">
   <si>
     <t>Filename</t>
   </si>
@@ -1061,6 +1062,27 @@
   </si>
   <si>
     <t>YES</t>
+  </si>
+  <si>
+    <t>Error group</t>
+  </si>
+  <si>
+    <t>Sheet</t>
+  </si>
+  <si>
+    <t>Error level</t>
+  </si>
+  <si>
+    <t>Row num</t>
+  </si>
+  <si>
+    <t>Variable</t>
+  </si>
+  <si>
+    <t>Error value</t>
+  </si>
+  <si>
+    <t>Dataset</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1248,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1292,6 +1314,7 @@
     <xf numFmtId="49" fontId="8" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2388,6 +2411,1454 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B645C89-E05F-455F-8D1D-76D1DA1878BA}">
+  <dimension ref="A1:V23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="7" max="8" width="12.42578125" customWidth="1"/>
+    <col min="10" max="10" width="13.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.85546875" customWidth="1"/>
+    <col min="12" max="12" width="13.85546875" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="16" max="16" width="13.85546875" customWidth="1"/>
+    <col min="17" max="17" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>308</v>
+      </c>
+      <c r="N1" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="O1" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="P1" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="Q1" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="R1" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="S1" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="T1" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="U1" s="16" t="s">
+        <v>313</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F2" s="17" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>337</v>
+      </c>
+      <c r="I2" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>318</v>
+      </c>
+      <c r="O2" s="17" t="s">
+        <v>319</v>
+      </c>
+      <c r="P2" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>320</v>
+      </c>
+      <c r="R2" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="L3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="M3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="N3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="O3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="R3" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="S3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="U3" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="V3" s="18" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>12</v>
+      </c>
+      <c r="B4" s="17">
+        <v>2</v>
+      </c>
+      <c r="C4" s="17">
+        <v>8</v>
+      </c>
+      <c r="D4" s="17">
+        <v>8</v>
+      </c>
+      <c r="E4" s="19">
+        <v>8</v>
+      </c>
+      <c r="F4" s="17">
+        <v>24</v>
+      </c>
+      <c r="G4" s="17">
+        <v>8</v>
+      </c>
+      <c r="H4" s="17">
+        <v>8</v>
+      </c>
+      <c r="I4" s="17">
+        <v>8</v>
+      </c>
+      <c r="J4" s="17">
+        <v>9</v>
+      </c>
+      <c r="K4" s="17">
+        <v>200</v>
+      </c>
+      <c r="L4" s="17">
+        <v>8</v>
+      </c>
+      <c r="M4" s="17">
+        <v>9</v>
+      </c>
+      <c r="N4" s="17">
+        <v>8</v>
+      </c>
+      <c r="O4" s="17">
+        <v>11</v>
+      </c>
+      <c r="P4" s="17">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="17">
+        <v>8</v>
+      </c>
+      <c r="R4" s="17">
+        <v>8</v>
+      </c>
+      <c r="S4" s="17">
+        <v>200</v>
+      </c>
+      <c r="T4" s="17">
+        <v>9</v>
+      </c>
+      <c r="U4" s="17">
+        <v>10</v>
+      </c>
+      <c r="V4" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="18">
+        <v>1</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H5" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I5" s="20">
+        <v>71</v>
+      </c>
+      <c r="J5" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="K5" s="20">
+        <v>71</v>
+      </c>
+      <c r="L5" s="18">
+        <v>71</v>
+      </c>
+      <c r="M5" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="N5" s="18"/>
+      <c r="O5" s="18"/>
+      <c r="P5" s="18"/>
+      <c r="Q5" s="18"/>
+      <c r="R5" s="18">
+        <v>1</v>
+      </c>
+      <c r="S5" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="T5" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="U5" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="V5" s="18">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="17">
+        <v>2</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I6" s="19">
+        <v>71</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="K6" s="19">
+        <v>71</v>
+      </c>
+      <c r="L6" s="17">
+        <v>71</v>
+      </c>
+      <c r="M6" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
+      <c r="R6" s="17">
+        <v>2</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>277</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>278</v>
+      </c>
+      <c r="V6" s="17">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="18">
+        <v>3</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H7" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I7" s="20">
+        <v>83</v>
+      </c>
+      <c r="J7" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="K7" s="20">
+        <v>83</v>
+      </c>
+      <c r="L7" s="18">
+        <v>83</v>
+      </c>
+      <c r="M7" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="N7" s="18"/>
+      <c r="O7" s="18"/>
+      <c r="P7" s="18" t="s">
+        <v>193</v>
+      </c>
+      <c r="Q7" s="18"/>
+      <c r="R7" s="18">
+        <v>3</v>
+      </c>
+      <c r="S7" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="T7" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="U7" s="18" t="s">
+        <v>264</v>
+      </c>
+      <c r="V7" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="17">
+        <v>4</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I8" s="19">
+        <v>79</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="K8" s="19">
+        <v>79</v>
+      </c>
+      <c r="L8" s="17">
+        <v>79</v>
+      </c>
+      <c r="M8" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="N8" s="17"/>
+      <c r="O8" s="17"/>
+      <c r="P8" s="17"/>
+      <c r="Q8" s="17"/>
+      <c r="R8" s="17">
+        <v>4</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="T8" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="V8" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="18">
+        <v>5</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H9" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I9" s="20">
+        <v>68</v>
+      </c>
+      <c r="J9" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="K9" s="20">
+        <v>68</v>
+      </c>
+      <c r="L9" s="18">
+        <v>68</v>
+      </c>
+      <c r="M9" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18">
+        <v>5</v>
+      </c>
+      <c r="S9" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="T9" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U9" s="18" t="s">
+        <v>283</v>
+      </c>
+      <c r="V9" s="18">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="17">
+        <v>6</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I10" s="19">
+        <v>77</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="K10" s="19">
+        <v>77</v>
+      </c>
+      <c r="L10" s="17">
+        <v>77</v>
+      </c>
+      <c r="M10" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="N10" s="17"/>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17">
+        <v>1</v>
+      </c>
+      <c r="R10" s="17">
+        <v>7</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="T10" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U10" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="V10" s="17">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="18">
+        <v>7</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H11" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I11" s="20">
+        <v>71</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="K11" s="20">
+        <v>71</v>
+      </c>
+      <c r="L11" s="18">
+        <v>71</v>
+      </c>
+      <c r="M11" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="N11" s="18"/>
+      <c r="O11" s="18"/>
+      <c r="P11" s="18"/>
+      <c r="Q11" s="18">
+        <v>2</v>
+      </c>
+      <c r="R11" s="18">
+        <v>7</v>
+      </c>
+      <c r="S11" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="V11" s="18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" s="17">
+        <v>8</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>324</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>325</v>
+      </c>
+      <c r="G12" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H12" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I12" s="19">
+        <v>69</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="K12" s="19">
+        <v>69</v>
+      </c>
+      <c r="L12" s="17">
+        <v>69</v>
+      </c>
+      <c r="M12" s="17" t="s">
+        <v>327</v>
+      </c>
+      <c r="N12" s="17"/>
+      <c r="O12" s="17"/>
+      <c r="P12" s="17"/>
+      <c r="Q12" s="17">
+        <v>3</v>
+      </c>
+      <c r="R12" s="17">
+        <v>7</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="T12" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="V12" s="17">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="18">
+        <v>9</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I13" s="20">
+        <v>76</v>
+      </c>
+      <c r="J13" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="K13" s="20">
+        <v>76</v>
+      </c>
+      <c r="L13" s="18">
+        <v>76</v>
+      </c>
+      <c r="M13" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="N13" s="18"/>
+      <c r="O13" s="18"/>
+      <c r="P13" s="18"/>
+      <c r="Q13" s="18">
+        <v>1</v>
+      </c>
+      <c r="R13" s="18">
+        <v>8</v>
+      </c>
+      <c r="S13" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="T13" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U13" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="V13" s="18">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="17">
+        <v>20</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="G14" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H14" s="18" t="s">
+        <v>338</v>
+      </c>
+      <c r="I14" s="19">
+        <v>51</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K14" s="19">
+        <v>51</v>
+      </c>
+      <c r="L14" s="17">
+        <v>51</v>
+      </c>
+      <c r="M14" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
+      <c r="P14" s="17"/>
+      <c r="Q14" s="17"/>
+      <c r="R14" s="17">
+        <v>5</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="T14" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U14" s="17" t="s">
+        <v>283</v>
+      </c>
+      <c r="V14" s="17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="18">
+        <v>21</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="20">
+        <v>52</v>
+      </c>
+      <c r="J15" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K15" s="20">
+        <v>52</v>
+      </c>
+      <c r="L15" s="18">
+        <v>52</v>
+      </c>
+      <c r="M15" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="N15" s="18"/>
+      <c r="O15" s="18"/>
+      <c r="P15" s="18"/>
+      <c r="Q15" s="18">
+        <v>1</v>
+      </c>
+      <c r="R15" s="18">
+        <v>7</v>
+      </c>
+      <c r="S15" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="T15" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U15" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="V15" s="18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="17">
+        <v>22</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="G16" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H16" s="17"/>
+      <c r="I16" s="19">
+        <v>62</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K16" s="19">
+        <v>62</v>
+      </c>
+      <c r="L16" s="17">
+        <v>62</v>
+      </c>
+      <c r="M16" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N16" s="17"/>
+      <c r="O16" s="17"/>
+      <c r="P16" s="17"/>
+      <c r="Q16" s="17">
+        <v>2</v>
+      </c>
+      <c r="R16" s="17">
+        <v>7</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>287</v>
+      </c>
+      <c r="T16" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="V16" s="17">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D17" s="18">
+        <v>23</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="20">
+        <v>62</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K17" s="20">
+        <v>62</v>
+      </c>
+      <c r="L17" s="18">
+        <v>62</v>
+      </c>
+      <c r="M17" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="N17" s="18"/>
+      <c r="O17" s="18"/>
+      <c r="P17" s="18"/>
+      <c r="Q17" s="18">
+        <v>3</v>
+      </c>
+      <c r="R17" s="18">
+        <v>7</v>
+      </c>
+      <c r="S17" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="T17" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U17" s="18" t="s">
+        <v>288</v>
+      </c>
+      <c r="V17" s="18">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="17">
+        <v>24</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="G18" s="17" t="s">
+        <v>329</v>
+      </c>
+      <c r="H18" s="17"/>
+      <c r="I18" s="19">
+        <v>50</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K18" s="19">
+        <v>50</v>
+      </c>
+      <c r="L18" s="17">
+        <v>50</v>
+      </c>
+      <c r="M18" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N18" s="17"/>
+      <c r="O18" s="17"/>
+      <c r="P18" s="17"/>
+      <c r="Q18" s="17">
+        <v>1</v>
+      </c>
+      <c r="R18" s="17">
+        <v>8</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="T18" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="V18" s="17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D19" s="18">
+        <v>25</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="20">
+        <v>52</v>
+      </c>
+      <c r="J19" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K19" s="20">
+        <v>52</v>
+      </c>
+      <c r="L19" s="18">
+        <v>52</v>
+      </c>
+      <c r="M19" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18">
+        <v>2</v>
+      </c>
+      <c r="R19" s="18">
+        <v>8</v>
+      </c>
+      <c r="S19" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="T19" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U19" s="18" t="s">
+        <v>290</v>
+      </c>
+      <c r="V19" s="18">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="17">
+        <v>26</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="G20" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H20" s="17"/>
+      <c r="I20" s="19">
+        <v>54</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K20" s="19">
+        <v>54</v>
+      </c>
+      <c r="L20" s="17">
+        <v>54</v>
+      </c>
+      <c r="M20" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N20" s="17"/>
+      <c r="O20" s="17"/>
+      <c r="P20" s="17"/>
+      <c r="Q20" s="17">
+        <v>3</v>
+      </c>
+      <c r="R20" s="17">
+        <v>8</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>289</v>
+      </c>
+      <c r="T20" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U20" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="V20" s="17">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D21" s="18">
+        <v>27</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="H21" s="18"/>
+      <c r="I21" s="20">
+        <v>79</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K21" s="20">
+        <v>79</v>
+      </c>
+      <c r="L21" s="18">
+        <v>79</v>
+      </c>
+      <c r="M21" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="18">
+        <v>1</v>
+      </c>
+      <c r="R21" s="18">
+        <v>201</v>
+      </c>
+      <c r="S21" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="T21" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U21" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="V21" s="18">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="17">
+        <v>28</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>330</v>
+      </c>
+      <c r="F22" s="17" t="s">
+        <v>331</v>
+      </c>
+      <c r="G22" s="17" t="s">
+        <v>326</v>
+      </c>
+      <c r="H22" s="17"/>
+      <c r="I22" s="19">
+        <v>98</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="K22" s="19">
+        <v>98</v>
+      </c>
+      <c r="L22" s="17">
+        <v>98</v>
+      </c>
+      <c r="M22" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="N22" s="17"/>
+      <c r="O22" s="17"/>
+      <c r="P22" s="17"/>
+      <c r="Q22" s="17">
+        <v>2</v>
+      </c>
+      <c r="R22" s="17">
+        <v>201</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="T22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="U22" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="V22" s="17">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="90" x14ac:dyDescent="0.25">
+      <c r="A23" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="D23" s="18">
+        <v>29</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G23" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H23" s="18"/>
+      <c r="I23" s="20">
+        <v>94</v>
+      </c>
+      <c r="J23" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="K23" s="20">
+        <v>94</v>
+      </c>
+      <c r="L23" s="18">
+        <v>94</v>
+      </c>
+      <c r="M23" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="N23" s="18"/>
+      <c r="O23" s="18"/>
+      <c r="P23" s="18"/>
+      <c r="Q23" s="18">
+        <v>3</v>
+      </c>
+      <c r="R23" s="18">
+        <v>201</v>
+      </c>
+      <c r="S23" s="18" t="s">
+        <v>293</v>
+      </c>
+      <c r="T23" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="U23" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="V23" s="18">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:V4">
+    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))&gt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B8"/>
@@ -2471,6 +3942,50 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BDDED82-7289-408A-8597-CE1381ED9DDD}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>339</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>341</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="F1" s="23" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:U8"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2964,7 +4479,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B41BDCC7-F382-49D0-BD18-4F06A3554CB3}">
   <dimension ref="A1:R18"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3800,7 +5315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E928109-8D06-4717-9DE5-10A023DB72D3}">
   <dimension ref="A1:X9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4449,7 +5964,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F69B0C80-0D21-48CC-B786-5AC734E98D04}">
   <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4949,7 +6464,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{803C895A-71FF-4E02-8999-07460F53FFBB}">
   <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5145,7 +6660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE85576-D13E-47AC-B7EE-857DE52A312D}">
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5629,1472 +7144,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B645C89-E05F-455F-8D1D-76D1DA1878BA}">
-  <dimension ref="A1:V23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="8" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="13.140625" customWidth="1"/>
-    <col min="11" max="11" width="12.85546875" customWidth="1"/>
-    <col min="12" max="12" width="13.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="16" max="16" width="13.85546875" customWidth="1"/>
-    <col min="17" max="17" width="13.42578125" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="16" t="s">
-        <v>300</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>301</v>
-      </c>
-      <c r="F1" s="16" t="s">
-        <v>302</v>
-      </c>
-      <c r="G1" s="16" t="s">
-        <v>303</v>
-      </c>
-      <c r="H1" s="22" t="s">
-        <v>336</v>
-      </c>
-      <c r="I1" s="16" t="s">
-        <v>304</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>308</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>309</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="P1" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="Q1" s="16" t="s">
-        <v>312</v>
-      </c>
-      <c r="R1" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="T1" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="U1" s="16" t="s">
-        <v>313</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="D2" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="F2" s="17" t="s">
-        <v>316</v>
-      </c>
-      <c r="G2" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="H2" s="17" t="s">
-        <v>337</v>
-      </c>
-      <c r="I2" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="J2" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="L2" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="M2" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="N2" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="O2" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="P2" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q2" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="R2" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="S2" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="T2" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="U2" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="V2" s="17" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="H3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="K3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="L3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="M3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="N3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="P3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="R3" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="S3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="T3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="V3" s="18" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="17">
-        <v>12</v>
-      </c>
-      <c r="B4" s="17">
-        <v>2</v>
-      </c>
-      <c r="C4" s="17">
-        <v>8</v>
-      </c>
-      <c r="D4" s="17">
-        <v>8</v>
-      </c>
-      <c r="E4" s="19">
-        <v>8</v>
-      </c>
-      <c r="F4" s="17">
-        <v>24</v>
-      </c>
-      <c r="G4" s="17">
-        <v>8</v>
-      </c>
-      <c r="H4" s="17">
-        <v>8</v>
-      </c>
-      <c r="I4" s="17">
-        <v>8</v>
-      </c>
-      <c r="J4" s="17">
-        <v>9</v>
-      </c>
-      <c r="K4" s="17">
-        <v>200</v>
-      </c>
-      <c r="L4" s="17">
-        <v>8</v>
-      </c>
-      <c r="M4" s="17">
-        <v>9</v>
-      </c>
-      <c r="N4" s="17">
-        <v>8</v>
-      </c>
-      <c r="O4" s="17">
-        <v>11</v>
-      </c>
-      <c r="P4" s="17">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="17">
-        <v>8</v>
-      </c>
-      <c r="R4" s="17">
-        <v>8</v>
-      </c>
-      <c r="S4" s="17">
-        <v>200</v>
-      </c>
-      <c r="T4" s="17">
-        <v>9</v>
-      </c>
-      <c r="U4" s="17">
-        <v>10</v>
-      </c>
-      <c r="V4" s="17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="18">
-        <v>1</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I5" s="20">
-        <v>71</v>
-      </c>
-      <c r="J5" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K5" s="20">
-        <v>71</v>
-      </c>
-      <c r="L5" s="18">
-        <v>71</v>
-      </c>
-      <c r="M5" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N5" s="18"/>
-      <c r="O5" s="18"/>
-      <c r="P5" s="18"/>
-      <c r="Q5" s="18"/>
-      <c r="R5" s="18">
-        <v>1</v>
-      </c>
-      <c r="S5" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="T5" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U5" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="V5" s="18">
-        <v>-7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D6" s="17">
-        <v>2</v>
-      </c>
-      <c r="E6" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H6" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I6" s="19">
-        <v>71</v>
-      </c>
-      <c r="J6" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K6" s="19">
-        <v>71</v>
-      </c>
-      <c r="L6" s="17">
-        <v>71</v>
-      </c>
-      <c r="M6" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N6" s="17"/>
-      <c r="O6" s="17"/>
-      <c r="P6" s="17"/>
-      <c r="Q6" s="17"/>
-      <c r="R6" s="17">
-        <v>2</v>
-      </c>
-      <c r="S6" s="17" t="s">
-        <v>277</v>
-      </c>
-      <c r="T6" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="U6" s="17" t="s">
-        <v>278</v>
-      </c>
-      <c r="V6" s="17">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="18">
-        <v>3</v>
-      </c>
-      <c r="E7" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G7" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H7" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I7" s="20">
-        <v>83</v>
-      </c>
-      <c r="J7" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K7" s="20">
-        <v>83</v>
-      </c>
-      <c r="L7" s="18">
-        <v>83</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N7" s="18"/>
-      <c r="O7" s="18"/>
-      <c r="P7" s="18" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q7" s="18"/>
-      <c r="R7" s="18">
-        <v>3</v>
-      </c>
-      <c r="S7" s="18" t="s">
-        <v>279</v>
-      </c>
-      <c r="T7" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="U7" s="18" t="s">
-        <v>264</v>
-      </c>
-      <c r="V7" s="18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="17">
-        <v>4</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H8" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I8" s="19">
-        <v>79</v>
-      </c>
-      <c r="J8" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K8" s="19">
-        <v>79</v>
-      </c>
-      <c r="L8" s="17">
-        <v>79</v>
-      </c>
-      <c r="M8" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="17">
-        <v>4</v>
-      </c>
-      <c r="S8" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="T8" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U8" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="V8" s="17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B9" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" s="18">
-        <v>5</v>
-      </c>
-      <c r="E9" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G9" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H9" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I9" s="20">
-        <v>68</v>
-      </c>
-      <c r="J9" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K9" s="20">
-        <v>68</v>
-      </c>
-      <c r="L9" s="18">
-        <v>68</v>
-      </c>
-      <c r="M9" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N9" s="18"/>
-      <c r="O9" s="18"/>
-      <c r="P9" s="18"/>
-      <c r="Q9" s="18"/>
-      <c r="R9" s="18">
-        <v>5</v>
-      </c>
-      <c r="S9" s="18" t="s">
-        <v>282</v>
-      </c>
-      <c r="T9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U9" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="V9" s="18">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="17">
-        <v>6</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>328</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G10" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="H10" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I10" s="19">
-        <v>77</v>
-      </c>
-      <c r="J10" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K10" s="19">
-        <v>77</v>
-      </c>
-      <c r="L10" s="17">
-        <v>77</v>
-      </c>
-      <c r="M10" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N10" s="17"/>
-      <c r="O10" s="17"/>
-      <c r="P10" s="17"/>
-      <c r="Q10" s="17">
-        <v>1</v>
-      </c>
-      <c r="R10" s="17">
-        <v>7</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T10" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U10" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V10" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C11" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D11" s="18">
-        <v>7</v>
-      </c>
-      <c r="E11" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G11" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H11" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I11" s="20">
-        <v>71</v>
-      </c>
-      <c r="J11" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K11" s="20">
-        <v>71</v>
-      </c>
-      <c r="L11" s="18">
-        <v>71</v>
-      </c>
-      <c r="M11" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18"/>
-      <c r="P11" s="18"/>
-      <c r="Q11" s="18">
-        <v>2</v>
-      </c>
-      <c r="R11" s="18">
-        <v>7</v>
-      </c>
-      <c r="S11" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T11" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U11" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V11" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="17">
-        <v>8</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="G12" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H12" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I12" s="19">
-        <v>69</v>
-      </c>
-      <c r="J12" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="K12" s="19">
-        <v>69</v>
-      </c>
-      <c r="L12" s="17">
-        <v>69</v>
-      </c>
-      <c r="M12" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="N12" s="17"/>
-      <c r="O12" s="17"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="17">
-        <v>3</v>
-      </c>
-      <c r="R12" s="17">
-        <v>7</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T12" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U12" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V12" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" ht="45" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B13" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C13" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="18">
-        <v>9</v>
-      </c>
-      <c r="E13" s="18" t="s">
-        <v>324</v>
-      </c>
-      <c r="F13" s="18" t="s">
-        <v>325</v>
-      </c>
-      <c r="G13" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H13" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I13" s="20">
-        <v>76</v>
-      </c>
-      <c r="J13" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="K13" s="20">
-        <v>76</v>
-      </c>
-      <c r="L13" s="18">
-        <v>76</v>
-      </c>
-      <c r="M13" s="18" t="s">
-        <v>327</v>
-      </c>
-      <c r="N13" s="18"/>
-      <c r="O13" s="18"/>
-      <c r="P13" s="18"/>
-      <c r="Q13" s="18">
-        <v>1</v>
-      </c>
-      <c r="R13" s="18">
-        <v>8</v>
-      </c>
-      <c r="S13" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="T13" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U13" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="V13" s="18">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="17">
-        <v>20</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H14" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="I14" s="19">
-        <v>51</v>
-      </c>
-      <c r="J14" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K14" s="19">
-        <v>51</v>
-      </c>
-      <c r="L14" s="17">
-        <v>51</v>
-      </c>
-      <c r="M14" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N14" s="17"/>
-      <c r="O14" s="17"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="17"/>
-      <c r="R14" s="17">
-        <v>5</v>
-      </c>
-      <c r="S14" s="17" t="s">
-        <v>282</v>
-      </c>
-      <c r="T14" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U14" s="17" t="s">
-        <v>283</v>
-      </c>
-      <c r="V14" s="17">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B15" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="18">
-        <v>21</v>
-      </c>
-      <c r="E15" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F15" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G15" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="20">
-        <v>52</v>
-      </c>
-      <c r="J15" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K15" s="20">
-        <v>52</v>
-      </c>
-      <c r="L15" s="18">
-        <v>52</v>
-      </c>
-      <c r="M15" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N15" s="18"/>
-      <c r="O15" s="18"/>
-      <c r="P15" s="18"/>
-      <c r="Q15" s="18">
-        <v>1</v>
-      </c>
-      <c r="R15" s="18">
-        <v>7</v>
-      </c>
-      <c r="S15" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T15" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U15" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V15" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" s="17">
-        <v>22</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H16" s="17"/>
-      <c r="I16" s="19">
-        <v>62</v>
-      </c>
-      <c r="J16" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K16" s="19">
-        <v>62</v>
-      </c>
-      <c r="L16" s="17">
-        <v>62</v>
-      </c>
-      <c r="M16" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N16" s="17"/>
-      <c r="O16" s="17"/>
-      <c r="P16" s="17"/>
-      <c r="Q16" s="17">
-        <v>2</v>
-      </c>
-      <c r="R16" s="17">
-        <v>7</v>
-      </c>
-      <c r="S16" s="17" t="s">
-        <v>287</v>
-      </c>
-      <c r="T16" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U16" s="17" t="s">
-        <v>288</v>
-      </c>
-      <c r="V16" s="17">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D17" s="18">
-        <v>23</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F17" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G17" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H17" s="18"/>
-      <c r="I17" s="20">
-        <v>62</v>
-      </c>
-      <c r="J17" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K17" s="20">
-        <v>62</v>
-      </c>
-      <c r="L17" s="18">
-        <v>62</v>
-      </c>
-      <c r="M17" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N17" s="18"/>
-      <c r="O17" s="18"/>
-      <c r="P17" s="18"/>
-      <c r="Q17" s="18">
-        <v>3</v>
-      </c>
-      <c r="R17" s="18">
-        <v>7</v>
-      </c>
-      <c r="S17" s="18" t="s">
-        <v>287</v>
-      </c>
-      <c r="T17" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U17" s="18" t="s">
-        <v>288</v>
-      </c>
-      <c r="V17" s="18">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="17">
-        <v>24</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="H18" s="17"/>
-      <c r="I18" s="19">
-        <v>50</v>
-      </c>
-      <c r="J18" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K18" s="19">
-        <v>50</v>
-      </c>
-      <c r="L18" s="17">
-        <v>50</v>
-      </c>
-      <c r="M18" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17">
-        <v>1</v>
-      </c>
-      <c r="R18" s="17">
-        <v>8</v>
-      </c>
-      <c r="S18" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="T18" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U18" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="V18" s="17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" s="18">
-        <v>25</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F19" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H19" s="18"/>
-      <c r="I19" s="20">
-        <v>52</v>
-      </c>
-      <c r="J19" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K19" s="20">
-        <v>52</v>
-      </c>
-      <c r="L19" s="18">
-        <v>52</v>
-      </c>
-      <c r="M19" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N19" s="18"/>
-      <c r="O19" s="18"/>
-      <c r="P19" s="18"/>
-      <c r="Q19" s="18">
-        <v>2</v>
-      </c>
-      <c r="R19" s="18">
-        <v>8</v>
-      </c>
-      <c r="S19" s="18" t="s">
-        <v>289</v>
-      </c>
-      <c r="T19" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U19" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="V19" s="18">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="17">
-        <v>26</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="19">
-        <v>54</v>
-      </c>
-      <c r="J20" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K20" s="19">
-        <v>54</v>
-      </c>
-      <c r="L20" s="17">
-        <v>54</v>
-      </c>
-      <c r="M20" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N20" s="17"/>
-      <c r="O20" s="17"/>
-      <c r="P20" s="17"/>
-      <c r="Q20" s="17">
-        <v>3</v>
-      </c>
-      <c r="R20" s="17">
-        <v>8</v>
-      </c>
-      <c r="S20" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="T20" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U20" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="V20" s="17">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A21" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C21" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D21" s="18">
-        <v>27</v>
-      </c>
-      <c r="E21" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G21" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="H21" s="18"/>
-      <c r="I21" s="20">
-        <v>79</v>
-      </c>
-      <c r="J21" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K21" s="20">
-        <v>79</v>
-      </c>
-      <c r="L21" s="18">
-        <v>79</v>
-      </c>
-      <c r="M21" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N21" s="18"/>
-      <c r="O21" s="18"/>
-      <c r="P21" s="18"/>
-      <c r="Q21" s="18">
-        <v>1</v>
-      </c>
-      <c r="R21" s="18">
-        <v>201</v>
-      </c>
-      <c r="S21" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="T21" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U21" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="V21" s="18">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="D22" s="17">
-        <v>28</v>
-      </c>
-      <c r="E22" s="17" t="s">
-        <v>330</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="G22" s="17" t="s">
-        <v>326</v>
-      </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="19">
-        <v>98</v>
-      </c>
-      <c r="J22" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="K22" s="19">
-        <v>98</v>
-      </c>
-      <c r="L22" s="17">
-        <v>98</v>
-      </c>
-      <c r="M22" s="17" t="s">
-        <v>332</v>
-      </c>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17">
-        <v>2</v>
-      </c>
-      <c r="R22" s="17">
-        <v>201</v>
-      </c>
-      <c r="S22" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="T22" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="U22" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="V22" s="17">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="90" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="B23" s="18" t="s">
-        <v>323</v>
-      </c>
-      <c r="C23" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="18">
-        <v>29</v>
-      </c>
-      <c r="E23" s="18" t="s">
-        <v>330</v>
-      </c>
-      <c r="F23" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="G23" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="H23" s="18"/>
-      <c r="I23" s="20">
-        <v>94</v>
-      </c>
-      <c r="J23" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="K23" s="20">
-        <v>94</v>
-      </c>
-      <c r="L23" s="18">
-        <v>94</v>
-      </c>
-      <c r="M23" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="N23" s="18"/>
-      <c r="O23" s="18"/>
-      <c r="P23" s="18"/>
-      <c r="Q23" s="18">
-        <v>3</v>
-      </c>
-      <c r="R23" s="18">
-        <v>201</v>
-      </c>
-      <c r="S23" s="18" t="s">
-        <v>293</v>
-      </c>
-      <c r="T23" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="U23" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="V23" s="18">
-        <v>172</v>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="A2:V4">
-    <cfRule type="notContainsBlanks" dxfId="0" priority="1">
-      <formula>LEN(TRIM(A2))&gt;0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010090ADB40D834AE945B19FCDA4041AC0CB" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="c09bae7b217a3930fedb3a6204001e96">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xmlns:ns3="63ea592b-d684-45c7-8cdc-fad8f8e6bb41" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ac018b55a0c98af8ca0cc741473a0b1c" ns2:_="" ns3:_="">
     <xsd:import namespace="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
@@ -7317,25 +7367,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D2B826-D4BB-4F95-9EB6-C2567A4D352D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <Comment xmlns="9dee18c2-6da5-44c1-913e-bf7f393fe0e8" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAA37260-A745-4F1A-87F7-7324275C4FF1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7352,4 +7401,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C3BEB11F-0E5C-4B66-89CC-AB3651412BF0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{68D2B826-D4BB-4F95-9EB6-C2567A4D352D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9dee18c2-6da5-44c1-913e-bf7f393fe0e8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>